--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6809R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6809R_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU2"/>
+  <dimension ref="A1:BU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,239 +781,480 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS6809-06-06-NWO-FG</t>
+          <t>FS6809-04-04-NWO-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="D2" t="n">
-        <v>0.735</v>
+        <v>0.65</v>
       </c>
       <c r="E2" t="n">
-        <v>0.261</v>
+        <v>0.201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.707</v>
+        <v>0.622</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3575</v>
+        <v>0.294</v>
       </c>
       <c r="H2" t="n">
-        <v>0.135</v>
+        <v>0.118</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4</v>
+        <v>0.335</v>
       </c>
       <c r="J2" t="n">
-        <v>0.392</v>
+        <v>0.337</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46765</v>
+        <v>0.39664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.375</v>
+        <v>0.325</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3465</v>
+        <v>0.2835</v>
       </c>
       <c r="N2" t="n">
-        <v>0.30992</v>
+        <v>0.25118</v>
       </c>
       <c r="O2" t="n">
-        <v>0.30432</v>
+        <v>0.26238</v>
       </c>
       <c r="P2" t="n">
         <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.361</v>
+        <v>0.2985</v>
       </c>
       <c r="R2" t="n">
-        <v>0.31</v>
+        <v>0.251</v>
       </c>
       <c r="S2" t="n">
-        <v>0.177</v>
+        <v>0.157</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.392</v>
+        <v>0.337</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3</v>
+        <v>0.2188</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.38</v>
+        <v>0.3175</v>
       </c>
       <c r="AB2" t="n">
         <v>75</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.44301</v>
+        <v>0.37084</v>
       </c>
       <c r="AD2" t="n">
         <v>75</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.16174</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.16174</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>FS6809-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Female Face Seal Swivel x Adjustable Male ORB Elbow - stud neck below the flats, 9/16-18 UN (female O-ring face-seal swivel, SAE J1453) x 7/16-20 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>FS6809R</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>7/16-20 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: L11@DRIVE] [BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L21@DRIVE: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "AAA LGTH" = "1.04" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; L10@DRIVE: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "N LGTH" = "1.29" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; SHEX@HEX: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "C1 HEX" = "0.687" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; Q-FS-NUT: = Air-Way FF318-4 S 0.69 to rounding; S3HEX@HEX: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "C2 HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "JJ FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; D19@BORE: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "A HOLE" = "0.165" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - swivel-end bore; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6809-16-16-NWO-FG 0.79 vs 0.783); D20@BORE: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "B HOLE" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 151.5, page verified True) [Brennan = yes 2026-10-18] - stud-end bore; mapping: same-table check: 1/3 rows with an Air-Way value agree to rounding (2 differ, e.g. FS6809-16-16-NWO-FG 0.85 vs 0.811); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "A THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -04 = 0.4375 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "7/16-20" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "A THREAD" "9/16-18" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p11 table ORFS-p011-t01 "FS6809-NWO-FG FFSS-MAORB 90 DEG ELBOW" row FS6809-04-04-NWO-FG col "B THREAD" "7/16-20" in the table's format | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on AAA LGTH=1.04 vs Air-Way L21=1.29 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6809 is used only where Brennan FS6809-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5697 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p11 FS6809-04-04-NWO-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6809-04-04-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: L11@DRIVE=N-DT; user 2026-10-21 "yes you can use them following my rule") | leg 2: adjustable stud tip -&gt; washer face 0.433 = L10 - L11 (Air-Way), thread 0.307 = stud - undercut 0.126, tip -&gt; body face 0.81 (FS lock nut 0.28 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>FS6809-04-04-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS6809-06-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="P3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.33</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AF3" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG3" t="n">
         <v>0.397</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH3" t="n">
         <v>0.035</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AI3" t="n">
         <v>0.2405</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AJ3" t="n">
         <v>0.28125</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK3" t="n">
         <v>0.367</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL3" t="n">
         <v>0.75</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AM3" t="n">
         <v>0.33</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN3" t="n">
         <v>0.26</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO3" t="n">
         <v>1.525</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AP3" t="n">
         <v>0.3</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AQ3" t="n">
         <v>1.45</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AR3" t="n">
         <v>0.6198399999999999</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS3" t="n">
         <v>0.3409</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AT3" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AU3" t="n">
         <v>0.30992</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AV3" t="n">
         <v>0.34375</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AW3" t="n">
         <v>1.525</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AX3" t="n">
         <v>0.5625</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AY3" t="n">
         <v>0.05556</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AZ3" t="n">
         <v>0.367</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BA3" t="n">
         <v>0.03007</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB3" t="n">
         <v>0.01389</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BC3" t="n">
         <v>0.05556</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BD3" t="n">
         <v>0.75</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BE3" t="n">
         <v>0.415</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BF3" t="n">
         <v>0.75</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BG3" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BH3" t="n">
         <v>0.375</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BI3" t="n">
         <v>0.375</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BJ3" t="n">
         <v>0.21601</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BK3" t="n">
         <v>0.21601</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BL3" t="n">
         <v>0.43251</v>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>FS6809-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>ORFS 90 deg Female Face Seal Swivel x Adjustable Male ORB Elbow - stud neck below the flats, 11/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>FS6809R</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6809 (s27, double-pass 2026-10-15, parts.air-way.com/api/series/27, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p11 FS6809-06-06-NWO-FG (ORFS-p011-t01); FORGED part: Air-Way NON-forged row FF6809-6-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>Air-Way FF6809 (s27, double-pass 2026-10-15, parts.air-way.com/api/series/27, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p11 FS6809-06-06-NWO-FG (ORFS-p011-t01); FORGED part: Air-Way NON-forged row FF6809-6-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
         <is>
           <t>forged (-FG): Air-Way non-forged FF6809-6-6 NWO = Brennan forged FS6809-06-06-NWO-FG p11 on every compared cell (AAA LGTH ~ L21, N LGTH ~ L10, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6809 is used only where Brennan FS6809-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5698 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.47 = L10 - L11 (Air-Way), thread 0.367 = stud - undercut 0.103, tip -&gt; body face 0.893 (FS lock nut 0.33 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.018 past the swivel body face (0.415) but stays inside the neck (max 0.124 off the axis vs neck radius 0.261) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 1 hex arm 0.415 barely clears the corner puck (radius 0.433)</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>FS6809-06-06-NWO-FG</t>
         </is>
